--- a/artfynd/A 55560-2023 artfynd.xlsx
+++ b/artfynd/A 55560-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114927493</v>
+        <v>114927486</v>
       </c>
       <c r="B2" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Öster om Långmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551131</v>
+        <v>551097</v>
       </c>
       <c r="R2" t="n">
-        <v>6522979</v>
+        <v>6522984</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -763,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,12 +775,7 @@
         <v>114927487</v>
       </c>
       <c r="B3" t="n">
-        <v>95203</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114927490</v>
+        <v>114927499</v>
       </c>
       <c r="B4" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551147</v>
+        <v>551063</v>
       </c>
       <c r="R4" t="n">
-        <v>6522987</v>
+        <v>6522920</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -986,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114927495</v>
+        <v>114927488</v>
       </c>
       <c r="B5" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551163</v>
+        <v>551114</v>
       </c>
       <c r="R5" t="n">
-        <v>6522993</v>
+        <v>6522928</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1088,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114927486</v>
+        <v>114927494</v>
       </c>
       <c r="B6" t="n">
-        <v>95203</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551097</v>
+        <v>551100</v>
       </c>
       <c r="R6" t="n">
-        <v>6522984</v>
+        <v>6522989</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1190,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114927488</v>
+        <v>114927495</v>
       </c>
       <c r="B7" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551114</v>
+        <v>551163</v>
       </c>
       <c r="R7" t="n">
-        <v>6522928</v>
+        <v>6522993</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1292,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114927499</v>
+        <v>114927490</v>
       </c>
       <c r="B8" t="n">
-        <v>94322</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2170</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551063</v>
+        <v>551147</v>
       </c>
       <c r="R8" t="n">
-        <v>6522920</v>
+        <v>6522987</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1394,50 +1354,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114927494</v>
+        <v>114927493</v>
       </c>
       <c r="B9" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Öster om Långmossen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551100</v>
+        <v>551131</v>
       </c>
       <c r="R9" t="n">
-        <v>6522989</v>
+        <v>6522979</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1478,6 +1437,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1493,6 +1453,109 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>114876355</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hällkärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>551249</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6523041</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skedevi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Louise Nilsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Louise Nilsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55560-2023 artfynd.xlsx
+++ b/artfynd/A 55560-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114927486</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114927487</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114927499</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114927488</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114927494</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114927495</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114927490</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114927493</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1556,8 +1601,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114876355</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>